--- a/output/pdf_financials_xlsx/ZLTO.xlsx
+++ b/output/pdf_financials_xlsx/ZLTO.xlsx
@@ -2954,10 +2954,10 @@
         <v>0.015437</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>0.012271</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>-0.001501</v>
       </c>
     </row>
     <row r="104">
@@ -3020,10 +3020,10 @@
         <v>0.020545</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.013614</v>
+        <v>0.025885</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.105933</v>
+        <v>0.104432</v>
       </c>
     </row>
     <row r="107">
@@ -3970,7 +3970,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -8025,7 +8029,11 @@
           <t>Decrease (Increase) in Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -9081,7 +9089,11 @@
           <t>Decrease in Prepaids and Deposits</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ZLTO.xlsx
+++ b/output/pdf_financials_xlsx/ZLTO.xlsx
@@ -2891,7 +2891,7 @@
         <v>0.001427</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.009852</v>
       </c>
     </row>
     <row r="101">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
